--- a/StructureDefinition-VunsPneumoBio.xlsx
+++ b/StructureDefinition-VunsPneumoBio.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2422" uniqueCount="521">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2415" uniqueCount="511">
   <si>
     <t>Property</t>
   </si>
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.1</t>
+    <t>0.1.2</t>
   </si>
   <si>
     <t>Name</t>
@@ -276,7 +276,7 @@
   </si>
   <si>
     <t>dom-2:If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
-dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}obs-7:If Observation.code is the same as an Observation.component.code then the value element associated with the code SHALL NOT be present {value.empty() or component.code.where(coding.intersect(%resource.code.coding).exists()).empty()}obs-6:dataAbsentReason SHALL only be present if Observation.value[x] is not present {dataAbsentReason.empty() or value.empty()}</t>
+dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}obs-6:dataAbsentReason SHALL only be present if Observation.value[x] is not present {dataAbsentReason.empty() or value.empty()}obs-7:If Observation.code is the same as an Observation.component.code then the value element associated with the code SHALL NOT be present {value.empty() or component.code.where(coding.intersect(%resource.code.coding).exists()).empty()}</t>
   </si>
   <si>
     <t>Event</t>
@@ -455,6 +455,259 @@
     <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
   </si>
   <si>
+    <t>DomainResource.extension</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
+  </si>
+  <si>
+    <t>Observation.modifierExtension</t>
+  </si>
+  <si>
+    <t>Extensions that cannot be ignored</t>
+  </si>
+  <si>
+    <t>May be used to represent additional information that is not part of the basic definition of the resource and that modifies the understanding of the element that contains it and/or the understanding of the containing element's descendants. Usually modifier elements provide negation or qualification. To make the use of extensions safe and manageable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer is allowed to define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension. Applications processing a resource are required to check for modifier extensions.
+Modifier extensions SHALL NOT change the meaning of any elements on Resource or DomainResource (including cannot change the meaning of modifierExtension itself).</t>
+  </si>
+  <si>
+    <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4/extensibility.html#modifierExtension).</t>
+  </si>
+  <si>
+    <t>DomainResource.modifierExtension</t>
+  </si>
+  <si>
+    <t>Observation.identifier</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Identifier
+</t>
+  </si>
+  <si>
+    <t>Business Identifier for observation</t>
+  </si>
+  <si>
+    <t>A unique identifier assigned to this observation.</t>
+  </si>
+  <si>
+    <t>Allows observations to be distinguished and referenced.</t>
+  </si>
+  <si>
+    <t>Event.identifier</t>
+  </si>
+  <si>
+    <t>OBX.21  For OBX segments from systems without OBX-21 support a combination of ORC/OBR and OBX must be negotiated between trading partners to uniquely identify the OBX segment. Depending on how V2 has been implemented each of these may be an option: 1) OBR-3 + OBX-3 + OBX-4 or 2) OBR-3 + OBR-4 + OBX-3 + OBX-4 or 2) some other way to uniquely ID the OBR/ORC + OBX-3 + OBX-4.</t>
+  </si>
+  <si>
+    <t>id</t>
+  </si>
+  <si>
+    <t>FiveWs.identifier</t>
+  </si>
+  <si>
+    <t>Observation.basedOn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fulfills
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(CarePlan|DeviceRequest|ImmunizationRecommendation|MedicationRequest|NutritionOrder|ServiceRequest)
+</t>
+  </si>
+  <si>
+    <t>Fulfills plan, proposal or order</t>
+  </si>
+  <si>
+    <t>A plan, proposal or order that is fulfilled in whole or in part by this event.  For example, a MedicationRequest may require a patient to have laboratory test performed before  it is dispensed.</t>
+  </si>
+  <si>
+    <t>Allows tracing of authorization for the event and tracking whether proposals/recommendations were acted upon.</t>
+  </si>
+  <si>
+    <t>Event.basedOn</t>
+  </si>
+  <si>
+    <t>ORC</t>
+  </si>
+  <si>
+    <t>.inboundRelationship[typeCode=COMP].source[moodCode=EVN]</t>
+  </si>
+  <si>
+    <t>Observation.partOf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Container
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(MedicationAdministration|MedicationDispense|MedicationStatement|Procedure|Immunization|ImagingStudy)
+</t>
+  </si>
+  <si>
+    <t>Part of referenced event</t>
+  </si>
+  <si>
+    <t>A larger event of which this particular Observation is a component or step.  For example,  an observation as part of a procedure.</t>
+  </si>
+  <si>
+    <t>To link an Observation to an Encounter use `encounter`.  See the  [Notes](http://hl7.org/fhir/R4/observation.html#obsgrouping) below for guidance on referencing another Observation.</t>
+  </si>
+  <si>
+    <t>Event.partOf</t>
+  </si>
+  <si>
+    <t>Varies by domain</t>
+  </si>
+  <si>
+    <t>.outboundRelationship[typeCode=FLFS].target</t>
+  </si>
+  <si>
+    <t>Observation.status</t>
+  </si>
+  <si>
+    <t>registered | preliminary | final | amended +</t>
+  </si>
+  <si>
+    <t>The status of the result value.</t>
+  </si>
+  <si>
+    <t>This element is labeled as a modifier because the status contains codes that mark the resource as not currently valid.</t>
+  </si>
+  <si>
+    <t>Need to track the status of individual results. Some results are finalized before the whole report is finalized.</t>
+  </si>
+  <si>
+    <t>final</t>
+  </si>
+  <si>
+    <t>required</t>
+  </si>
+  <si>
+    <t>Codes providing the status of an observation.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/observation-status|4.0.1</t>
+  </si>
+  <si>
+    <t>Event.status</t>
+  </si>
+  <si>
+    <t>&lt; 445584004 |Report by finality status|</t>
+  </si>
+  <si>
+    <t>OBX-11</t>
+  </si>
+  <si>
+    <t>status  Amended &amp; Final are differentiated by whether it is the subject of a ControlAct event with a type of "revise"</t>
+  </si>
+  <si>
+    <t>FiveWs.status</t>
+  </si>
+  <si>
+    <t>Observation.category</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CodeableConcept
+</t>
+  </si>
+  <si>
+    <t>Classification of  type of observation</t>
+  </si>
+  <si>
+    <t>A code that classifies the general type of observation being made.</t>
+  </si>
+  <si>
+    <t>In addition to the required category valueset, this element allows various categorization schemes based on the owner’s definition of the category and effectively multiple categories can be used at once.  The level of granularity is defined by the category concepts in the value set.</t>
+  </si>
+  <si>
+    <t>Used for filtering what observations are retrieved and displayed.</t>
+  </si>
+  <si>
+    <t>Codes for high level observation categories.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/observation-category</t>
+  </si>
+  <si>
+    <t>.outboundRelationship[typeCode="COMP].target[classCode="LIST", moodCode="EVN"].code</t>
+  </si>
+  <si>
+    <t>FiveWs.class</t>
+  </si>
+  <si>
+    <t>Observation.code</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Name
+</t>
+  </si>
+  <si>
+    <t>Type of observation (code / type)</t>
+  </si>
+  <si>
+    <t>Describes what was observed. Sometimes this is called the observation "name".</t>
+  </si>
+  <si>
+    <t>*All* code-value and, if present, component.code-component.value pairs need to be taken into account to correctly understand the meaning of the observation.</t>
+  </si>
+  <si>
+    <t>Knowing what kind of observation is being made is essential to understanding the observation.</t>
+  </si>
+  <si>
+    <t>example</t>
+  </si>
+  <si>
+    <t>Codes identifying names of simple observations.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/observation-codes</t>
+  </si>
+  <si>
+    <t>Event.code</t>
+  </si>
+  <si>
+    <t>&lt; 363787002 |Observable entity| OR &lt; 386053000 |Evaluation procedure|</t>
+  </si>
+  <si>
+    <t>OBX-3</t>
+  </si>
+  <si>
+    <t>code</t>
+  </si>
+  <si>
+    <t>FiveWs.what[x]</t>
+  </si>
+  <si>
+    <t>116680003 |Is a|</t>
+  </si>
+  <si>
+    <t>Observation.code.id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">string
+</t>
+  </si>
+  <si>
+    <t>Unique id for inter-element referencing</t>
+  </si>
+  <si>
+    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
+  </si>
+  <si>
+    <t>Element.id</t>
+  </si>
+  <si>
+    <t>n/a</t>
+  </si>
+  <si>
+    <t>Observation.code.extension</t>
+  </si>
+  <si>
+    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
+  </si>
+  <si>
     <t xml:space="preserve">value:url}
 </t>
   </si>
@@ -465,273 +718,6 @@
     <t>open</t>
   </si>
   <si>
-    <t>DomainResource.extension</t>
-  </si>
-  <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
-  </si>
-  <si>
-    <t>Observation.modifierExtension</t>
-  </si>
-  <si>
-    <t>Extensions that cannot be ignored</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the resource and that modifies the understanding of the element that contains it and/or the understanding of the containing element's descendants. Usually modifier elements provide negation or qualification. To make the use of extensions safe and manageable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer is allowed to define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension. Applications processing a resource are required to check for modifier extensions.
-Modifier extensions SHALL NOT change the meaning of any elements on Resource or DomainResource (including cannot change the meaning of modifierExtension itself).</t>
-  </si>
-  <si>
-    <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4/extensibility.html#modifierExtension).</t>
-  </si>
-  <si>
-    <t>DomainResource.modifierExtension</t>
-  </si>
-  <si>
-    <t>Observation.identifier</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Identifier
-</t>
-  </si>
-  <si>
-    <t>Business Identifier for observation</t>
-  </si>
-  <si>
-    <t>A unique identifier assigned to this observation.</t>
-  </si>
-  <si>
-    <t>Allows observations to be distinguished and referenced.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ele-1
-</t>
-  </si>
-  <si>
-    <t>Event.identifier</t>
-  </si>
-  <si>
-    <t>OBX.21  For OBX segments from systems without OBX-21 support a combination of ORC/OBR and OBX must be negotiated between trading partners to uniquely identify the OBX segment. Depending on how V2 has been implemented each of these may be an option: 1) OBR-3 + OBX-3 + OBX-4 or 2) OBR-3 + OBR-4 + OBX-3 + OBX-4 or 2) some other way to uniquely ID the OBR/ORC + OBX-3 + OBX-4.</t>
-  </si>
-  <si>
-    <t>id</t>
-  </si>
-  <si>
-    <t>FiveWs.identifier</t>
-  </si>
-  <si>
-    <t>Observation.basedOn</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fulfills
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(CarePlan|DeviceRequest|ImmunizationRecommendation|MedicationRequest|NutritionOrder|ServiceRequest)
-</t>
-  </si>
-  <si>
-    <t>Fulfills plan, proposal or order</t>
-  </si>
-  <si>
-    <t>A plan, proposal or order that is fulfilled in whole or in part by this event.  For example, a MedicationRequest may require a patient to have laboratory test performed before  it is dispensed.</t>
-  </si>
-  <si>
-    <t>References SHALL be a reference to an actual FHIR resource, and SHALL be resolveable (allowing for access control, temporary unavailability, etc.). Resolution can be either by retrieval from the URL, or, where applicable by resource type, by treating an absolute reference as a canonical URL and looking it up in a local registry/repository.</t>
-  </si>
-  <si>
-    <t>Allows tracing of authorization for the event and tracking whether proposals/recommendations were acted upon.</t>
-  </si>
-  <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-ref-1:SHALL have a contained resource if a local reference is provided {reference.startsWith('#').not() or (reference.substring(1).trace('url') in %rootResource.contained.id.trace('ids'))}</t>
-  </si>
-  <si>
-    <t>Event.basedOn</t>
-  </si>
-  <si>
-    <t>ORC</t>
-  </si>
-  <si>
-    <t>.inboundRelationship[typeCode=COMP].source[moodCode=EVN]</t>
-  </si>
-  <si>
-    <t>Observation.partOf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Container
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(MedicationAdministration|MedicationDispense|MedicationStatement|Procedure|Immunization|ImagingStudy)
-</t>
-  </si>
-  <si>
-    <t>Part of referenced event</t>
-  </si>
-  <si>
-    <t>A larger event of which this particular Observation is a component or step.  For example,  an observation as part of a procedure.</t>
-  </si>
-  <si>
-    <t>To link an Observation to an Encounter use `encounter`.  See the  [Notes](http://hl7.org/fhir/R4/observation.html#obsgrouping) below for guidance on referencing another Observation.</t>
-  </si>
-  <si>
-    <t>Event.partOf</t>
-  </si>
-  <si>
-    <t>Varies by domain</t>
-  </si>
-  <si>
-    <t>.outboundRelationship[typeCode=FLFS].target</t>
-  </si>
-  <si>
-    <t>Observation.status</t>
-  </si>
-  <si>
-    <t>registered | preliminary | final | amended +</t>
-  </si>
-  <si>
-    <t>The status of the result value.</t>
-  </si>
-  <si>
-    <t>This element is labeled as a modifier because the status contains codes that mark the resource as not currently valid.</t>
-  </si>
-  <si>
-    <t>Need to track the status of individual results. Some results are finalized before the whole report is finalized.</t>
-  </si>
-  <si>
-    <t>final</t>
-  </si>
-  <si>
-    <t>required</t>
-  </si>
-  <si>
-    <t>Codes providing the status of an observation.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-status|4.0.1</t>
-  </si>
-  <si>
-    <t>Event.status</t>
-  </si>
-  <si>
-    <t>&lt; 445584004 |Report by finality status|</t>
-  </si>
-  <si>
-    <t>OBX-11</t>
-  </si>
-  <si>
-    <t>status  Amended &amp; Final are differentiated by whether it is the subject of a ControlAct event with a type of "revise"</t>
-  </si>
-  <si>
-    <t>FiveWs.status</t>
-  </si>
-  <si>
-    <t>Observation.category</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CodeableConcept
-</t>
-  </si>
-  <si>
-    <t>Classification of  type of observation</t>
-  </si>
-  <si>
-    <t>A code that classifies the general type of observation being made.</t>
-  </si>
-  <si>
-    <t>In addition to the required category valueset, this element allows various categorization schemes based on the owner’s definition of the category and effectively multiple categories can be used at once.  The level of granularity is defined by the category concepts in the value set.</t>
-  </si>
-  <si>
-    <t>Used for filtering what observations are retrieved and displayed.</t>
-  </si>
-  <si>
-    <t>Codes for high level observation categories.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-category</t>
-  </si>
-  <si>
-    <t>CE/CNE/CWE</t>
-  </si>
-  <si>
-    <t>.outboundRelationship[typeCode="COMP].target[classCode="LIST", moodCode="EVN"].code</t>
-  </si>
-  <si>
-    <t>FiveWs.class</t>
-  </si>
-  <si>
-    <t>Observation.code</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Name
-</t>
-  </si>
-  <si>
-    <t>Type of observation (code / type)</t>
-  </si>
-  <si>
-    <t>Describes what was observed. Sometimes this is called the observation "name".</t>
-  </si>
-  <si>
-    <t>*All* code-value and, if present, component.code-component.value pairs need to be taken into account to correctly understand the meaning of the observation.</t>
-  </si>
-  <si>
-    <t>Knowing what kind of observation is being made is essential to understanding the observation.</t>
-  </si>
-  <si>
-    <t>example</t>
-  </si>
-  <si>
-    <t>Codes identifying names of simple observations.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-codes</t>
-  </si>
-  <si>
-    <t>Event.code</t>
-  </si>
-  <si>
-    <t>&lt; 363787002 |Observable entity| OR &lt; 386053000 |Evaluation procedure|</t>
-  </si>
-  <si>
-    <t>OBX-3</t>
-  </si>
-  <si>
-    <t>code</t>
-  </si>
-  <si>
-    <t>FiveWs.what[x]</t>
-  </si>
-  <si>
-    <t>116680003 |Is a|</t>
-  </si>
-  <si>
-    <t>Observation.code.id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">string
-</t>
-  </si>
-  <si>
-    <t>Unique id for inter-element referencing</t>
-  </si>
-  <si>
-    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
-  </si>
-  <si>
-    <t>Element.id</t>
-  </si>
-  <si>
-    <t>n/a</t>
-  </si>
-  <si>
-    <t>Observation.code.extension</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
-  </si>
-  <si>
     <t>Element.extension</t>
   </si>
   <si>
@@ -847,9 +833,6 @@
     <t>A representation of the meaning of the code in the system, following the rules of the system.</t>
   </si>
   <si>
-    <t>Note that FHIR strings SHALL NOT exceed 1MB in size</t>
-  </si>
-  <si>
     <t>Need to be able to carry a human-readable meaning of the code for readers that do not know  the system.</t>
   </si>
   <si>
@@ -1106,8 +1089,8 @@
     <t>An observation exists to have a value, though it might not if it is in error, or if it represents a group of observations.</t>
   </si>
   <si>
-    <t>ele-1
-obs-7</t>
+    <t xml:space="preserve">obs-7
+</t>
   </si>
   <si>
     <t>&lt; 441742003 |Evaluation finding|</t>
@@ -1147,8 +1130,8 @@
     <t>http://hl7.org/fhir/ValueSet/data-absent-reason</t>
   </si>
   <si>
-    <t>ele-1
-obs-6</t>
+    <t xml:space="preserve">obs-6
+</t>
   </si>
   <si>
     <t>value.nullFlavor</t>
@@ -1395,15 +1378,8 @@
     <t>The value of the low bound of the reference range.  The low bound of the reference range endpoint is inclusive of the value (e.g.  reference range is &gt;=5 - &lt;=9). If the low bound is omitted,  it is assumed to be meaningless (e.g. reference range is &lt;=2.3).</t>
   </si>
   <si>
-    <t>The context of use may frequently define what kind of quantity this is and therefore what kind of units can be used. The context of use may also restrict the values for the comparator.</t>
-  </si>
-  <si>
-    <t>ele-1
-obs-3</t>
-  </si>
-  <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-qty-3:If a code for the unit is present, the system SHALL also be present {code.empty() or system.exists()}sqty-1:The comparator is not used on a SimpleQuantity {comparator.empty()}</t>
+    <t xml:space="preserve">obs-3
+</t>
   </si>
   <si>
     <t>OBX-7</t>
@@ -1491,17 +1467,7 @@
     <t>The age at which this reference range is applicable. This is a neonatal age (e.g. number of weeks at term) if the meaning says so.</t>
   </si>
   <si>
-    <t>The stated low and high value are assumed to have arbitrarily high precision when it comes to determining which values are in the range. I.e. 1.99 is not in the range 2 -&gt; 3.</t>
-  </si>
-  <si>
     <t>Some analytes vary greatly over age.</t>
-  </si>
-  <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-rng-2:If present, low SHALL have a lower value than high {low.empty() or high.empty() or (low &lt;= high)}</t>
-  </si>
-  <si>
-    <t>NR and also possibly SN (but see also quantity)</t>
   </si>
   <si>
     <t>outboundRelationship[typeCode=PRCN].targetObservationCriterion[code="age"].value</t>
@@ -3029,19 +2995,19 @@
         <v>19</v>
       </c>
       <c r="AB9" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AC9" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AD9" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AE9" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AF9" t="s" s="2">
         <v>142</v>
-      </c>
-      <c r="AC9" t="s" s="2">
-        <v>143</v>
-      </c>
-      <c r="AD9" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AE9" t="s" s="2">
-        <v>144</v>
-      </c>
-      <c r="AF9" t="s" s="2">
-        <v>145</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>80</v>
@@ -3053,7 +3019,7 @@
         <v>19</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="AK9" t="s" s="2">
         <v>19</v>
@@ -3076,10 +3042,10 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
@@ -3105,16 +3071,16 @@
         <v>138</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="N10" t="s" s="2">
         <v>141</v>
       </c>
       <c r="O10" t="s" s="2">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="P10" t="s" s="2">
         <v>19</v>
@@ -3151,19 +3117,19 @@
         <v>19</v>
       </c>
       <c r="AB10" t="s" s="2">
-        <v>142</v>
+        <v>19</v>
       </c>
       <c r="AC10" t="s" s="2">
-        <v>143</v>
+        <v>19</v>
       </c>
       <c r="AD10" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AE10" t="s" s="2">
-        <v>144</v>
+        <v>19</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>80</v>
@@ -3175,7 +3141,7 @@
         <v>19</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="AK10" t="s" s="2">
         <v>19</v>
@@ -3198,10 +3164,10 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -3224,17 +3190,17 @@
         <v>93</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="N11" s="2"/>
       <c r="O11" t="s" s="2">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="P11" t="s" s="2">
         <v>19</v>
@@ -3283,7 +3249,7 @@
         <v>19</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>80</v>
@@ -3292,25 +3258,25 @@
         <v>81</v>
       </c>
       <c r="AI11" t="s" s="2">
-        <v>157</v>
+        <v>19</v>
       </c>
       <c r="AJ11" t="s" s="2">
         <v>104</v>
       </c>
       <c r="AK11" t="s" s="2">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="AL11" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AM11" t="s" s="2">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="AN11" t="s" s="2">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="AO11" t="s" s="2">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="AP11" t="s" s="2">
         <v>19</v>
@@ -3318,14 +3284,14 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="E12" s="2"/>
       <c r="F12" t="s" s="2">
@@ -3344,19 +3310,17 @@
         <v>93</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>166</v>
-      </c>
-      <c r="N12" t="s" s="2">
-        <v>167</v>
-      </c>
+        <v>162</v>
+      </c>
+      <c r="N12" s="2"/>
       <c r="O12" t="s" s="2">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="P12" t="s" s="2">
         <v>19</v>
@@ -3405,7 +3369,7 @@
         <v>19</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>80</v>
@@ -3414,22 +3378,22 @@
         <v>81</v>
       </c>
       <c r="AI12" t="s" s="2">
-        <v>157</v>
+        <v>19</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>169</v>
+        <v>104</v>
       </c>
       <c r="AK12" t="s" s="2">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="AL12" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AM12" t="s" s="2">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="AN12" t="s" s="2">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="AO12" t="s" s="2">
         <v>19</v>
@@ -3440,14 +3404,14 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="E13" s="2"/>
       <c r="F13" t="s" s="2">
@@ -3466,16 +3430,16 @@
         <v>93</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>175</v>
+        <v>169</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>176</v>
+        <v>170</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>178</v>
+        <v>172</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -3525,7 +3489,7 @@
         <v>19</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>80</v>
@@ -3534,22 +3498,22 @@
         <v>81</v>
       </c>
       <c r="AI13" t="s" s="2">
-        <v>157</v>
+        <v>19</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>169</v>
+        <v>104</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>179</v>
+        <v>173</v>
       </c>
       <c r="AL13" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AM13" t="s" s="2">
-        <v>180</v>
+        <v>174</v>
       </c>
       <c r="AN13" t="s" s="2">
-        <v>181</v>
+        <v>175</v>
       </c>
       <c r="AO13" t="s" s="2">
         <v>19</v>
@@ -3560,10 +3524,10 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>182</v>
+        <v>176</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>182</v>
+        <v>176</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -3589,16 +3553,16 @@
         <v>112</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>183</v>
+        <v>177</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>184</v>
+        <v>178</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>185</v>
+        <v>179</v>
       </c>
       <c r="O14" t="s" s="2">
-        <v>186</v>
+        <v>180</v>
       </c>
       <c r="P14" t="s" s="2">
         <v>19</v>
@@ -3608,7 +3572,7 @@
         <v>19</v>
       </c>
       <c r="S14" t="s" s="2">
-        <v>187</v>
+        <v>181</v>
       </c>
       <c r="T14" t="s" s="2">
         <v>19</v>
@@ -3623,13 +3587,13 @@
         <v>19</v>
       </c>
       <c r="X14" t="s" s="2">
-        <v>188</v>
+        <v>182</v>
       </c>
       <c r="Y14" t="s" s="2">
-        <v>189</v>
+        <v>183</v>
       </c>
       <c r="Z14" t="s" s="2">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="AA14" t="s" s="2">
         <v>19</v>
@@ -3647,7 +3611,7 @@
         <v>19</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>182</v>
+        <v>176</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>92</v>
@@ -3662,19 +3626,19 @@
         <v>104</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>191</v>
+        <v>185</v>
       </c>
       <c r="AL14" t="s" s="2">
-        <v>192</v>
+        <v>186</v>
       </c>
       <c r="AM14" t="s" s="2">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="AN14" t="s" s="2">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="AO14" t="s" s="2">
-        <v>195</v>
+        <v>189</v>
       </c>
       <c r="AP14" t="s" s="2">
         <v>19</v>
@@ -3682,10 +3646,10 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3708,19 +3672,19 @@
         <v>19</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>198</v>
+        <v>192</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>199</v>
+        <v>193</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>200</v>
+        <v>194</v>
       </c>
       <c r="O15" t="s" s="2">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="P15" t="s" s="2">
         <v>19</v>
@@ -3748,10 +3712,10 @@
         <v>116</v>
       </c>
       <c r="Y15" t="s" s="2">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="Z15" t="s" s="2">
-        <v>203</v>
+        <v>197</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>19</v>
@@ -3769,7 +3733,7 @@
         <v>19</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>80</v>
@@ -3778,7 +3742,7 @@
         <v>81</v>
       </c>
       <c r="AI15" t="s" s="2">
-        <v>157</v>
+        <v>19</v>
       </c>
       <c r="AJ15" t="s" s="2">
         <v>104</v>
@@ -3790,13 +3754,13 @@
         <v>19</v>
       </c>
       <c r="AM15" t="s" s="2">
-        <v>204</v>
+        <v>19</v>
       </c>
       <c r="AN15" t="s" s="2">
-        <v>205</v>
+        <v>198</v>
       </c>
       <c r="AO15" t="s" s="2">
-        <v>206</v>
+        <v>199</v>
       </c>
       <c r="AP15" t="s" s="2">
         <v>19</v>
@@ -3804,14 +3768,14 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>207</v>
+        <v>200</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>207</v>
+        <v>200</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>208</v>
+        <v>201</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
@@ -3830,19 +3794,19 @@
         <v>93</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>209</v>
+        <v>202</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>210</v>
+        <v>203</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>211</v>
+        <v>204</v>
       </c>
       <c r="O16" t="s" s="2">
-        <v>212</v>
+        <v>205</v>
       </c>
       <c r="P16" t="s" s="2">
         <v>19</v>
@@ -3867,13 +3831,13 @@
         <v>19</v>
       </c>
       <c r="X16" t="s" s="2">
-        <v>213</v>
+        <v>206</v>
       </c>
       <c r="Y16" t="s" s="2">
-        <v>214</v>
+        <v>207</v>
       </c>
       <c r="Z16" t="s" s="2">
-        <v>215</v>
+        <v>208</v>
       </c>
       <c r="AA16" t="s" s="2">
         <v>19</v>
@@ -3891,7 +3855,7 @@
         <v>19</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>207</v>
+        <v>200</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>92</v>
@@ -3900,36 +3864,36 @@
         <v>92</v>
       </c>
       <c r="AI16" t="s" s="2">
-        <v>157</v>
+        <v>19</v>
       </c>
       <c r="AJ16" t="s" s="2">
         <v>104</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>216</v>
+        <v>209</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>217</v>
+        <v>210</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>218</v>
+        <v>211</v>
       </c>
       <c r="AN16" t="s" s="2">
-        <v>219</v>
+        <v>212</v>
       </c>
       <c r="AO16" t="s" s="2">
-        <v>220</v>
+        <v>213</v>
       </c>
       <c r="AP16" t="s" s="2">
-        <v>221</v>
+        <v>214</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>222</v>
+        <v>215</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>222</v>
+        <v>215</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3952,13 +3916,13 @@
         <v>19</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>223</v>
+        <v>216</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>225</v>
+        <v>218</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -4009,7 +3973,7 @@
         <v>19</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>226</v>
+        <v>219</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>80</v>
@@ -4033,7 +3997,7 @@
         <v>19</v>
       </c>
       <c r="AN17" t="s" s="2">
-        <v>227</v>
+        <v>220</v>
       </c>
       <c r="AO17" t="s" s="2">
         <v>19</v>
@@ -4044,10 +4008,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>228</v>
+        <v>221</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>228</v>
+        <v>221</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -4076,7 +4040,7 @@
         <v>139</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>229</v>
+        <v>222</v>
       </c>
       <c r="N18" t="s" s="2">
         <v>141</v>
@@ -4117,19 +4081,19 @@
         <v>19</v>
       </c>
       <c r="AB18" t="s" s="2">
-        <v>142</v>
+        <v>223</v>
       </c>
       <c r="AC18" t="s" s="2">
-        <v>143</v>
+        <v>224</v>
       </c>
       <c r="AD18" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AE18" t="s" s="2">
-        <v>144</v>
+        <v>225</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>80</v>
@@ -4141,7 +4105,7 @@
         <v>19</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="AK18" t="s" s="2">
         <v>19</v>
@@ -4153,7 +4117,7 @@
         <v>19</v>
       </c>
       <c r="AN18" t="s" s="2">
-        <v>227</v>
+        <v>220</v>
       </c>
       <c r="AO18" t="s" s="2">
         <v>19</v>
@@ -4164,10 +4128,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -4190,19 +4154,19 @@
         <v>93</v>
       </c>
       <c r="K19" t="s" s="2">
+        <v>228</v>
+      </c>
+      <c r="L19" t="s" s="2">
+        <v>229</v>
+      </c>
+      <c r="M19" t="s" s="2">
+        <v>230</v>
+      </c>
+      <c r="N19" t="s" s="2">
+        <v>231</v>
+      </c>
+      <c r="O19" t="s" s="2">
         <v>232</v>
-      </c>
-      <c r="L19" t="s" s="2">
-        <v>233</v>
-      </c>
-      <c r="M19" t="s" s="2">
-        <v>234</v>
-      </c>
-      <c r="N19" t="s" s="2">
-        <v>235</v>
-      </c>
-      <c r="O19" t="s" s="2">
-        <v>236</v>
       </c>
       <c r="P19" t="s" s="2">
         <v>19</v>
@@ -4251,7 +4215,7 @@
         <v>19</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>80</v>
@@ -4260,7 +4224,7 @@
         <v>81</v>
       </c>
       <c r="AI19" t="s" s="2">
-        <v>157</v>
+        <v>19</v>
       </c>
       <c r="AJ19" t="s" s="2">
         <v>104</v>
@@ -4272,10 +4236,10 @@
         <v>19</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="AO19" t="s" s="2">
         <v>19</v>
@@ -4286,10 +4250,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4312,13 +4276,13 @@
         <v>19</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>223</v>
+        <v>216</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>225</v>
+        <v>218</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -4369,7 +4333,7 @@
         <v>19</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>226</v>
+        <v>219</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>80</v>
@@ -4393,7 +4357,7 @@
         <v>19</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>227</v>
+        <v>220</v>
       </c>
       <c r="AO20" t="s" s="2">
         <v>19</v>
@@ -4404,10 +4368,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4436,7 +4400,7 @@
         <v>139</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>229</v>
+        <v>222</v>
       </c>
       <c r="N21" t="s" s="2">
         <v>141</v>
@@ -4477,19 +4441,19 @@
         <v>19</v>
       </c>
       <c r="AB21" t="s" s="2">
-        <v>142</v>
+        <v>223</v>
       </c>
       <c r="AC21" t="s" s="2">
-        <v>143</v>
+        <v>224</v>
       </c>
       <c r="AD21" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AE21" t="s" s="2">
-        <v>144</v>
+        <v>225</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>80</v>
@@ -4501,7 +4465,7 @@
         <v>19</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="AK21" t="s" s="2">
         <v>19</v>
@@ -4513,7 +4477,7 @@
         <v>19</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>227</v>
+        <v>220</v>
       </c>
       <c r="AO21" t="s" s="2">
         <v>19</v>
@@ -4524,10 +4488,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4553,16 +4517,16 @@
         <v>106</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="O22" t="s" s="2">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="P22" t="s" s="2">
         <v>19</v>
@@ -4611,7 +4575,7 @@
         <v>19</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>80</v>
@@ -4632,10 +4596,10 @@
         <v>19</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="AO22" t="s" s="2">
         <v>19</v>
@@ -4646,10 +4610,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4672,16 +4636,16 @@
         <v>93</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>223</v>
+        <v>216</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
@@ -4731,7 +4695,7 @@
         <v>19</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>80</v>
@@ -4752,10 +4716,10 @@
         <v>19</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="AO23" t="s" s="2">
         <v>19</v>
@@ -4766,10 +4730,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4795,14 +4759,14 @@
         <v>112</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" t="s" s="2">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>19</v>
@@ -4827,11 +4791,11 @@
         <v>19</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>188</v>
+        <v>182</v>
       </c>
       <c r="Y24" s="2"/>
       <c r="Z24" t="s" s="2">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>19</v>
@@ -4849,7 +4813,7 @@
         <v>19</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>80</v>
@@ -4870,10 +4834,10 @@
         <v>19</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="AO24" t="s" s="2">
         <v>19</v>
@@ -4884,10 +4848,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4910,19 +4874,17 @@
         <v>93</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>223</v>
+        <v>216</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>267</v>
-      </c>
-      <c r="N25" t="s" s="2">
-        <v>268</v>
-      </c>
+        <v>263</v>
+      </c>
+      <c r="N25" s="2"/>
       <c r="O25" t="s" s="2">
-        <v>269</v>
+        <v>264</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>19</v>
@@ -4971,7 +4933,7 @@
         <v>19</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>270</v>
+        <v>265</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>80</v>
@@ -4992,10 +4954,10 @@
         <v>19</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>272</v>
+        <v>267</v>
       </c>
       <c r="AO25" t="s" s="2">
         <v>19</v>
@@ -5006,10 +4968,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>273</v>
+        <v>268</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>273</v>
+        <v>268</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5032,19 +4994,19 @@
         <v>93</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>274</v>
+        <v>269</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>275</v>
+        <v>270</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>276</v>
+        <v>271</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>277</v>
+        <v>272</v>
       </c>
       <c r="O26" t="s" s="2">
-        <v>278</v>
+        <v>273</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>19</v>
@@ -5093,7 +5055,7 @@
         <v>19</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>279</v>
+        <v>274</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>80</v>
@@ -5114,10 +5076,10 @@
         <v>19</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>280</v>
+        <v>275</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>281</v>
+        <v>276</v>
       </c>
       <c r="AO26" t="s" s="2">
         <v>19</v>
@@ -5128,10 +5090,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>282</v>
+        <v>277</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>282</v>
+        <v>277</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5154,19 +5116,19 @@
         <v>93</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>223</v>
+        <v>216</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>283</v>
+        <v>278</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>284</v>
+        <v>279</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="O27" t="s" s="2">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>19</v>
@@ -5215,7 +5177,7 @@
         <v>19</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>80</v>
@@ -5236,10 +5198,10 @@
         <v>19</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>288</v>
+        <v>283</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>289</v>
+        <v>284</v>
       </c>
       <c r="AO27" t="s" s="2">
         <v>19</v>
@@ -5250,10 +5212,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>290</v>
+        <v>285</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>290</v>
+        <v>285</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5276,19 +5238,19 @@
         <v>93</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>291</v>
+        <v>286</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>292</v>
+        <v>287</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>293</v>
+        <v>288</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>294</v>
+        <v>289</v>
       </c>
       <c r="O28" t="s" s="2">
-        <v>295</v>
+        <v>290</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>19</v>
@@ -5337,7 +5299,7 @@
         <v>19</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>290</v>
+        <v>285</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>80</v>
@@ -5346,25 +5308,25 @@
         <v>92</v>
       </c>
       <c r="AI28" t="s" s="2">
-        <v>157</v>
+        <v>19</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>169</v>
+        <v>104</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>296</v>
+        <v>291</v>
       </c>
       <c r="AL28" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>297</v>
+        <v>292</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>298</v>
+        <v>293</v>
       </c>
       <c r="AO28" t="s" s="2">
-        <v>299</v>
+        <v>294</v>
       </c>
       <c r="AP28" t="s" s="2">
         <v>19</v>
@@ -5372,10 +5334,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>300</v>
+        <v>295</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>300</v>
+        <v>295</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5398,16 +5360,16 @@
         <v>93</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>301</v>
+        <v>296</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>302</v>
+        <v>297</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>303</v>
+        <v>298</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>304</v>
+        <v>299</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
@@ -5457,7 +5419,7 @@
         <v>19</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>300</v>
+        <v>295</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>80</v>
@@ -5466,10 +5428,10 @@
         <v>81</v>
       </c>
       <c r="AI29" t="s" s="2">
-        <v>157</v>
+        <v>19</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>169</v>
+        <v>104</v>
       </c>
       <c r="AK29" t="s" s="2">
         <v>19</v>
@@ -5478,13 +5440,13 @@
         <v>19</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>218</v>
+        <v>211</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>305</v>
+        <v>300</v>
       </c>
       <c r="AO29" t="s" s="2">
-        <v>299</v>
+        <v>294</v>
       </c>
       <c r="AP29" t="s" s="2">
         <v>19</v>
@@ -5492,14 +5454,14 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>306</v>
+        <v>301</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>306</v>
+        <v>301</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
-        <v>307</v>
+        <v>302</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
@@ -5518,19 +5480,19 @@
         <v>93</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>308</v>
+        <v>303</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>309</v>
+        <v>304</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>310</v>
+        <v>305</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>311</v>
+        <v>306</v>
       </c>
       <c r="O30" t="s" s="2">
-        <v>312</v>
+        <v>307</v>
       </c>
       <c r="P30" t="s" s="2">
         <v>19</v>
@@ -5579,7 +5541,7 @@
         <v>19</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>306</v>
+        <v>301</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>80</v>
@@ -5588,25 +5550,25 @@
         <v>92</v>
       </c>
       <c r="AI30" t="s" s="2">
-        <v>157</v>
+        <v>19</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>169</v>
+        <v>104</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>313</v>
+        <v>308</v>
       </c>
       <c r="AL30" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>314</v>
+        <v>309</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>315</v>
+        <v>310</v>
       </c>
       <c r="AO30" t="s" s="2">
-        <v>316</v>
+        <v>311</v>
       </c>
       <c r="AP30" t="s" s="2">
         <v>19</v>
@@ -5614,14 +5576,14 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>317</v>
+        <v>312</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>317</v>
+        <v>312</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
-        <v>318</v>
+        <v>313</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
@@ -5640,19 +5602,19 @@
         <v>93</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>319</v>
+        <v>314</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>320</v>
+        <v>315</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="O31" t="s" s="2">
-        <v>323</v>
+        <v>318</v>
       </c>
       <c r="P31" t="s" s="2">
         <v>19</v>
@@ -5701,7 +5663,7 @@
         <v>19</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>317</v>
+        <v>312</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>80</v>
@@ -5710,25 +5672,25 @@
         <v>92</v>
       </c>
       <c r="AI31" t="s" s="2">
-        <v>157</v>
+        <v>19</v>
       </c>
       <c r="AJ31" t="s" s="2">
         <v>104</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="AL31" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>325</v>
+        <v>320</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>326</v>
+        <v>321</v>
       </c>
       <c r="AO31" t="s" s="2">
-        <v>327</v>
+        <v>322</v>
       </c>
       <c r="AP31" t="s" s="2">
         <v>19</v>
@@ -5736,10 +5698,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>328</v>
+        <v>323</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>328</v>
+        <v>323</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5762,16 +5724,16 @@
         <v>93</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>329</v>
+        <v>324</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>330</v>
+        <v>325</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>331</v>
+        <v>326</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>332</v>
+        <v>327</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -5821,7 +5783,7 @@
         <v>19</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>328</v>
+        <v>323</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>80</v>
@@ -5842,13 +5804,13 @@
         <v>19</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>333</v>
+        <v>328</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>334</v>
+        <v>329</v>
       </c>
       <c r="AO32" t="s" s="2">
-        <v>335</v>
+        <v>330</v>
       </c>
       <c r="AP32" t="s" s="2">
         <v>19</v>
@@ -5856,10 +5818,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>336</v>
+        <v>331</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>336</v>
+        <v>331</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5882,19 +5844,17 @@
         <v>93</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>337</v>
+        <v>332</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>338</v>
+        <v>333</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>339</v>
-      </c>
-      <c r="N33" t="s" s="2">
-        <v>167</v>
-      </c>
+        <v>334</v>
+      </c>
+      <c r="N33" s="2"/>
       <c r="O33" t="s" s="2">
-        <v>340</v>
+        <v>335</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>19</v>
@@ -5943,7 +5903,7 @@
         <v>19</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>336</v>
+        <v>331</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>80</v>
@@ -5952,25 +5912,25 @@
         <v>81</v>
       </c>
       <c r="AI33" t="s" s="2">
-        <v>157</v>
+        <v>19</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>169</v>
+        <v>104</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>341</v>
+        <v>336</v>
       </c>
       <c r="AL33" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>342</v>
+        <v>337</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>343</v>
+        <v>338</v>
       </c>
       <c r="AO33" t="s" s="2">
-        <v>344</v>
+        <v>339</v>
       </c>
       <c r="AP33" t="s" s="2">
         <v>19</v>
@@ -5978,10 +5938,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>345</v>
+        <v>340</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>345</v>
+        <v>340</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6004,19 +5964,19 @@
         <v>93</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>346</v>
+        <v>341</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>347</v>
+        <v>342</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>348</v>
+        <v>343</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>349</v>
+        <v>344</v>
       </c>
       <c r="O34" t="s" s="2">
-        <v>350</v>
+        <v>345</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>19</v>
@@ -6065,7 +6025,7 @@
         <v>19</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>345</v>
+        <v>340</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>80</v>
@@ -6074,7 +6034,7 @@
         <v>92</v>
       </c>
       <c r="AI34" t="s" s="2">
-        <v>351</v>
+        <v>346</v>
       </c>
       <c r="AJ34" t="s" s="2">
         <v>104</v>
@@ -6083,27 +6043,27 @@
         <v>19</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>352</v>
+        <v>347</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>353</v>
+        <v>348</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>354</v>
+        <v>349</v>
       </c>
       <c r="AO34" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AP34" t="s" s="2">
-        <v>355</v>
+        <v>350</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6126,19 +6086,19 @@
         <v>19</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>357</v>
+        <v>352</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>358</v>
+        <v>353</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>359</v>
+        <v>354</v>
       </c>
       <c r="O35" t="s" s="2">
-        <v>360</v>
+        <v>355</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>19</v>
@@ -6163,13 +6123,13 @@
         <v>19</v>
       </c>
       <c r="X35" t="s" s="2">
-        <v>361</v>
+        <v>356</v>
       </c>
       <c r="Y35" t="s" s="2">
-        <v>362</v>
+        <v>357</v>
       </c>
       <c r="Z35" t="s" s="2">
-        <v>363</v>
+        <v>358</v>
       </c>
       <c r="AA35" t="s" s="2">
         <v>19</v>
@@ -6187,7 +6147,7 @@
         <v>19</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>80</v>
@@ -6196,7 +6156,7 @@
         <v>92</v>
       </c>
       <c r="AI35" t="s" s="2">
-        <v>364</v>
+        <v>359</v>
       </c>
       <c r="AJ35" t="s" s="2">
         <v>104</v>
@@ -6211,7 +6171,7 @@
         <v>135</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>365</v>
+        <v>360</v>
       </c>
       <c r="AO35" t="s" s="2">
         <v>19</v>
@@ -6222,14 +6182,14 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>366</v>
+        <v>361</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>366</v>
+        <v>361</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
-        <v>367</v>
+        <v>362</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
@@ -6248,19 +6208,19 @@
         <v>19</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>369</v>
+        <v>364</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="O36" t="s" s="2">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>19</v>
@@ -6285,31 +6245,31 @@
         <v>19</v>
       </c>
       <c r="X36" t="s" s="2">
+        <v>356</v>
+      </c>
+      <c r="Y36" t="s" s="2">
+        <v>367</v>
+      </c>
+      <c r="Z36" t="s" s="2">
+        <v>368</v>
+      </c>
+      <c r="AA36" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AB36" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AC36" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AD36" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AE36" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AF36" t="s" s="2">
         <v>361</v>
-      </c>
-      <c r="Y36" t="s" s="2">
-        <v>372</v>
-      </c>
-      <c r="Z36" t="s" s="2">
-        <v>373</v>
-      </c>
-      <c r="AA36" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AB36" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AC36" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AD36" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AE36" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AF36" t="s" s="2">
-        <v>366</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>80</v>
@@ -6318,7 +6278,7 @@
         <v>81</v>
       </c>
       <c r="AI36" t="s" s="2">
-        <v>157</v>
+        <v>19</v>
       </c>
       <c r="AJ36" t="s" s="2">
         <v>104</v>
@@ -6327,27 +6287,27 @@
         <v>19</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>374</v>
+        <v>369</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>375</v>
+        <v>370</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>376</v>
+        <v>371</v>
       </c>
       <c r="AO36" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AP36" t="s" s="2">
-        <v>377</v>
+        <v>372</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>378</v>
+        <v>373</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>378</v>
+        <v>373</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6370,19 +6330,19 @@
         <v>19</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>379</v>
+        <v>374</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>380</v>
+        <v>375</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>381</v>
+        <v>376</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>382</v>
+        <v>377</v>
       </c>
       <c r="O37" t="s" s="2">
-        <v>383</v>
+        <v>378</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>19</v>
@@ -6431,7 +6391,7 @@
         <v>19</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>378</v>
+        <v>373</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
@@ -6440,7 +6400,7 @@
         <v>81</v>
       </c>
       <c r="AI37" t="s" s="2">
-        <v>157</v>
+        <v>19</v>
       </c>
       <c r="AJ37" t="s" s="2">
         <v>104</v>
@@ -6452,10 +6412,10 @@
         <v>19</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>384</v>
+        <v>379</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>385</v>
+        <v>380</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>19</v>
@@ -6466,10 +6426,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>386</v>
+        <v>381</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>386</v>
+        <v>381</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6492,16 +6452,16 @@
         <v>19</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>387</v>
+        <v>382</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>388</v>
+        <v>383</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>389</v>
+        <v>384</v>
       </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
@@ -6527,13 +6487,13 @@
         <v>19</v>
       </c>
       <c r="X38" t="s" s="2">
-        <v>213</v>
+        <v>206</v>
       </c>
       <c r="Y38" t="s" s="2">
-        <v>390</v>
+        <v>385</v>
       </c>
       <c r="Z38" t="s" s="2">
-        <v>391</v>
+        <v>386</v>
       </c>
       <c r="AA38" t="s" s="2">
         <v>19</v>
@@ -6551,7 +6511,7 @@
         <v>19</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>386</v>
+        <v>381</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>80</v>
@@ -6560,7 +6520,7 @@
         <v>92</v>
       </c>
       <c r="AI38" t="s" s="2">
-        <v>157</v>
+        <v>19</v>
       </c>
       <c r="AJ38" t="s" s="2">
         <v>104</v>
@@ -6569,27 +6529,27 @@
         <v>19</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>392</v>
+        <v>387</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>393</v>
+        <v>388</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>394</v>
+        <v>389</v>
       </c>
       <c r="AO38" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AP38" t="s" s="2">
-        <v>395</v>
+        <v>390</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>396</v>
+        <v>391</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>396</v>
+        <v>391</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6612,19 +6572,19 @@
         <v>19</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>397</v>
+        <v>392</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>398</v>
+        <v>393</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>399</v>
+        <v>394</v>
       </c>
       <c r="O39" t="s" s="2">
-        <v>400</v>
+        <v>395</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>19</v>
@@ -6649,13 +6609,13 @@
         <v>19</v>
       </c>
       <c r="X39" t="s" s="2">
-        <v>213</v>
+        <v>206</v>
       </c>
       <c r="Y39" t="s" s="2">
-        <v>401</v>
+        <v>396</v>
       </c>
       <c r="Z39" t="s" s="2">
-        <v>402</v>
+        <v>397</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>19</v>
@@ -6673,7 +6633,7 @@
         <v>19</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>396</v>
+        <v>391</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>80</v>
@@ -6682,7 +6642,7 @@
         <v>92</v>
       </c>
       <c r="AI39" t="s" s="2">
-        <v>157</v>
+        <v>19</v>
       </c>
       <c r="AJ39" t="s" s="2">
         <v>104</v>
@@ -6694,10 +6654,10 @@
         <v>19</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>403</v>
+        <v>398</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>404</v>
+        <v>399</v>
       </c>
       <c r="AO39" t="s" s="2">
         <v>19</v>
@@ -6708,10 +6668,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>405</v>
+        <v>400</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>405</v>
+        <v>400</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6734,16 +6694,16 @@
         <v>19</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>406</v>
+        <v>401</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>407</v>
+        <v>402</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>408</v>
+        <v>403</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>409</v>
+        <v>404</v>
       </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
@@ -6793,7 +6753,7 @@
         <v>19</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>405</v>
+        <v>400</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>80</v>
@@ -6802,36 +6762,36 @@
         <v>92</v>
       </c>
       <c r="AI40" t="s" s="2">
-        <v>157</v>
+        <v>19</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>169</v>
+        <v>104</v>
       </c>
       <c r="AK40" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>410</v>
+        <v>405</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>411</v>
+        <v>406</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>412</v>
+        <v>407</v>
       </c>
       <c r="AO40" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AP40" t="s" s="2">
-        <v>413</v>
+        <v>408</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>414</v>
+        <v>409</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>414</v>
+        <v>409</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6854,16 +6814,16 @@
         <v>19</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>415</v>
+        <v>410</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>416</v>
+        <v>411</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>417</v>
+        <v>412</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>418</v>
+        <v>413</v>
       </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
@@ -6913,7 +6873,7 @@
         <v>19</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>414</v>
+        <v>409</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>80</v>
@@ -6922,36 +6882,36 @@
         <v>92</v>
       </c>
       <c r="AI41" t="s" s="2">
-        <v>157</v>
+        <v>19</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>169</v>
+        <v>104</v>
       </c>
       <c r="AK41" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>419</v>
+        <v>414</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>420</v>
+        <v>415</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>421</v>
+        <v>416</v>
       </c>
       <c r="AO41" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AP41" t="s" s="2">
-        <v>422</v>
+        <v>417</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>423</v>
+        <v>418</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>423</v>
+        <v>418</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6974,19 +6934,19 @@
         <v>19</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>424</v>
+        <v>419</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>425</v>
+        <v>420</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>426</v>
+        <v>421</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>427</v>
+        <v>422</v>
       </c>
       <c r="O42" t="s" s="2">
-        <v>428</v>
+        <v>423</v>
       </c>
       <c r="P42" t="s" s="2">
         <v>19</v>
@@ -7035,7 +6995,7 @@
         <v>19</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>423</v>
+        <v>418</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
@@ -7044,10 +7004,10 @@
         <v>81</v>
       </c>
       <c r="AI42" t="s" s="2">
-        <v>157</v>
+        <v>19</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>429</v>
+        <v>424</v>
       </c>
       <c r="AK42" t="s" s="2">
         <v>19</v>
@@ -7056,10 +7016,10 @@
         <v>19</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>430</v>
+        <v>425</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>431</v>
+        <v>426</v>
       </c>
       <c r="AO42" t="s" s="2">
         <v>19</v>
@@ -7070,10 +7030,10 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>432</v>
+        <v>427</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>432</v>
+        <v>427</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7096,13 +7056,13 @@
         <v>19</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>223</v>
+        <v>216</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>225</v>
+        <v>218</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -7153,7 +7113,7 @@
         <v>19</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>226</v>
+        <v>219</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
@@ -7177,7 +7137,7 @@
         <v>19</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>227</v>
+        <v>220</v>
       </c>
       <c r="AO43" t="s" s="2">
         <v>19</v>
@@ -7188,10 +7148,10 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>433</v>
+        <v>428</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>433</v>
+        <v>428</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7220,7 +7180,7 @@
         <v>139</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>229</v>
+        <v>222</v>
       </c>
       <c r="N44" t="s" s="2">
         <v>141</v>
@@ -7261,19 +7221,19 @@
         <v>19</v>
       </c>
       <c r="AB44" t="s" s="2">
-        <v>142</v>
+        <v>19</v>
       </c>
       <c r="AC44" t="s" s="2">
-        <v>143</v>
+        <v>19</v>
       </c>
       <c r="AD44" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AE44" t="s" s="2">
-        <v>144</v>
+        <v>19</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
@@ -7285,7 +7245,7 @@
         <v>19</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="AK44" t="s" s="2">
         <v>19</v>
@@ -7297,7 +7257,7 @@
         <v>19</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>227</v>
+        <v>220</v>
       </c>
       <c r="AO44" t="s" s="2">
         <v>19</v>
@@ -7308,14 +7268,14 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>434</v>
+        <v>429</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>434</v>
+        <v>429</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
-        <v>435</v>
+        <v>430</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
@@ -7337,16 +7297,16 @@
         <v>138</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>436</v>
+        <v>431</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>437</v>
+        <v>432</v>
       </c>
       <c r="N45" t="s" s="2">
         <v>141</v>
       </c>
       <c r="O45" t="s" s="2">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>19</v>
@@ -7395,7 +7355,7 @@
         <v>19</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>438</v>
+        <v>433</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
@@ -7407,7 +7367,7 @@
         <v>19</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="AK45" t="s" s="2">
         <v>19</v>
@@ -7430,10 +7390,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>439</v>
+        <v>434</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>439</v>
+        <v>434</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7456,17 +7416,15 @@
         <v>19</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>440</v>
+        <v>435</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>441</v>
+        <v>436</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>442</v>
-      </c>
-      <c r="N46" t="s" s="2">
-        <v>443</v>
-      </c>
+        <v>437</v>
+      </c>
+      <c r="N46" s="2"/>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
         <v>19</v>
@@ -7515,7 +7473,7 @@
         <v>19</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>439</v>
+        <v>434</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
@@ -7524,10 +7482,10 @@
         <v>92</v>
       </c>
       <c r="AI46" t="s" s="2">
-        <v>444</v>
+        <v>438</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>445</v>
+        <v>104</v>
       </c>
       <c r="AK46" t="s" s="2">
         <v>19</v>
@@ -7536,10 +7494,10 @@
         <v>19</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>446</v>
+        <v>439</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>447</v>
+        <v>440</v>
       </c>
       <c r="AO46" t="s" s="2">
         <v>19</v>
@@ -7550,10 +7508,10 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>448</v>
+        <v>441</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>448</v>
+        <v>441</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7576,17 +7534,15 @@
         <v>19</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>440</v>
+        <v>435</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>449</v>
+        <v>442</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>450</v>
-      </c>
-      <c r="N47" t="s" s="2">
         <v>443</v>
       </c>
+      <c r="N47" s="2"/>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
         <v>19</v>
@@ -7635,7 +7591,7 @@
         <v>19</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>448</v>
+        <v>441</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
@@ -7644,22 +7600,22 @@
         <v>92</v>
       </c>
       <c r="AI47" t="s" s="2">
+        <v>438</v>
+      </c>
+      <c r="AJ47" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="AK47" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AL47" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AM47" t="s" s="2">
+        <v>439</v>
+      </c>
+      <c r="AN47" t="s" s="2">
         <v>444</v>
-      </c>
-      <c r="AJ47" t="s" s="2">
-        <v>445</v>
-      </c>
-      <c r="AK47" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AL47" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AM47" t="s" s="2">
-        <v>446</v>
-      </c>
-      <c r="AN47" t="s" s="2">
-        <v>451</v>
       </c>
       <c r="AO47" t="s" s="2">
         <v>19</v>
@@ -7670,10 +7626,10 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>452</v>
+        <v>445</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>452</v>
+        <v>445</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7696,19 +7652,19 @@
         <v>19</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>453</v>
+        <v>446</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>454</v>
+        <v>447</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>455</v>
+        <v>448</v>
       </c>
       <c r="O48" t="s" s="2">
-        <v>456</v>
+        <v>449</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>19</v>
@@ -7736,10 +7692,10 @@
         <v>116</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>457</v>
+        <v>450</v>
       </c>
       <c r="Z48" t="s" s="2">
-        <v>458</v>
+        <v>451</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>19</v>
@@ -7757,7 +7713,7 @@
         <v>19</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>452</v>
+        <v>445</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
@@ -7766,7 +7722,7 @@
         <v>92</v>
       </c>
       <c r="AI48" t="s" s="2">
-        <v>157</v>
+        <v>19</v>
       </c>
       <c r="AJ48" t="s" s="2">
         <v>104</v>
@@ -7775,13 +7731,13 @@
         <v>19</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>459</v>
+        <v>452</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>460</v>
+        <v>453</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>376</v>
+        <v>371</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>19</v>
@@ -7792,10 +7748,10 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>461</v>
+        <v>454</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>461</v>
+        <v>454</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7818,19 +7774,19 @@
         <v>19</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>462</v>
+        <v>455</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>463</v>
+        <v>456</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>464</v>
+        <v>457</v>
       </c>
       <c r="O49" t="s" s="2">
-        <v>465</v>
+        <v>458</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>19</v>
@@ -7855,13 +7811,13 @@
         <v>19</v>
       </c>
       <c r="X49" t="s" s="2">
-        <v>213</v>
+        <v>206</v>
       </c>
       <c r="Y49" t="s" s="2">
-        <v>466</v>
+        <v>459</v>
       </c>
       <c r="Z49" t="s" s="2">
-        <v>467</v>
+        <v>460</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>19</v>
@@ -7879,7 +7835,7 @@
         <v>19</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>461</v>
+        <v>454</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
@@ -7888,7 +7844,7 @@
         <v>81</v>
       </c>
       <c r="AI49" t="s" s="2">
-        <v>157</v>
+        <v>19</v>
       </c>
       <c r="AJ49" t="s" s="2">
         <v>104</v>
@@ -7897,13 +7853,13 @@
         <v>19</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>459</v>
+        <v>452</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>460</v>
+        <v>453</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>376</v>
+        <v>371</v>
       </c>
       <c r="AO49" t="s" s="2">
         <v>19</v>
@@ -7914,10 +7870,10 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>468</v>
+        <v>461</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>468</v>
+        <v>461</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7940,19 +7896,17 @@
         <v>19</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>469</v>
+        <v>462</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>470</v>
+        <v>463</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>471</v>
-      </c>
-      <c r="N50" t="s" s="2">
-        <v>472</v>
-      </c>
+        <v>464</v>
+      </c>
+      <c r="N50" s="2"/>
       <c r="O50" t="s" s="2">
-        <v>473</v>
+        <v>465</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>19</v>
@@ -8001,7 +7955,7 @@
         <v>19</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>468</v>
+        <v>461</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
@@ -8010,10 +7964,10 @@
         <v>92</v>
       </c>
       <c r="AI50" t="s" s="2">
-        <v>157</v>
+        <v>19</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>474</v>
+        <v>104</v>
       </c>
       <c r="AK50" t="s" s="2">
         <v>19</v>
@@ -8022,10 +7976,10 @@
         <v>19</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>475</v>
+        <v>19</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>476</v>
+        <v>466</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>19</v>
@@ -8036,10 +7990,10 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>477</v>
+        <v>467</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>477</v>
+        <v>467</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8062,17 +8016,15 @@
         <v>19</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>223</v>
+        <v>216</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>478</v>
+        <v>468</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>479</v>
-      </c>
-      <c r="N51" t="s" s="2">
-        <v>268</v>
-      </c>
+        <v>469</v>
+      </c>
+      <c r="N51" s="2"/>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
         <v>19</v>
@@ -8121,7 +8073,7 @@
         <v>19</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>477</v>
+        <v>467</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
@@ -8142,10 +8094,10 @@
         <v>19</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>446</v>
+        <v>439</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>480</v>
+        <v>470</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>19</v>
@@ -8156,10 +8108,10 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>481</v>
+        <v>471</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>481</v>
+        <v>471</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8182,16 +8134,16 @@
         <v>93</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>482</v>
+        <v>472</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>483</v>
+        <v>473</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>484</v>
+        <v>474</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>485</v>
+        <v>475</v>
       </c>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
@@ -8241,7 +8193,7 @@
         <v>19</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>481</v>
+        <v>471</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
@@ -8250,10 +8202,10 @@
         <v>81</v>
       </c>
       <c r="AI52" t="s" s="2">
-        <v>157</v>
+        <v>19</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>169</v>
+        <v>104</v>
       </c>
       <c r="AK52" t="s" s="2">
         <v>19</v>
@@ -8262,10 +8214,10 @@
         <v>19</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>486</v>
+        <v>476</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>487</v>
+        <v>477</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>19</v>
@@ -8276,10 +8228,10 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>488</v>
+        <v>478</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>488</v>
+        <v>478</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8302,16 +8254,16 @@
         <v>93</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>489</v>
+        <v>479</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>490</v>
+        <v>480</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>491</v>
+        <v>481</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>492</v>
+        <v>482</v>
       </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
@@ -8361,7 +8313,7 @@
         <v>19</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>488</v>
+        <v>478</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
@@ -8370,10 +8322,10 @@
         <v>81</v>
       </c>
       <c r="AI53" t="s" s="2">
-        <v>157</v>
+        <v>19</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>169</v>
+        <v>104</v>
       </c>
       <c r="AK53" t="s" s="2">
         <v>19</v>
@@ -8382,10 +8334,10 @@
         <v>19</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>486</v>
+        <v>476</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>493</v>
+        <v>483</v>
       </c>
       <c r="AO53" t="s" s="2">
         <v>19</v>
@@ -8396,10 +8348,10 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>494</v>
+        <v>484</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>494</v>
+        <v>484</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8422,19 +8374,19 @@
         <v>93</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>424</v>
+        <v>419</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>495</v>
+        <v>485</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>496</v>
+        <v>486</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>497</v>
+        <v>487</v>
       </c>
       <c r="O54" t="s" s="2">
-        <v>498</v>
+        <v>488</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>19</v>
@@ -8483,7 +8435,7 @@
         <v>19</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>494</v>
+        <v>484</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>80</v>
@@ -8492,7 +8444,7 @@
         <v>81</v>
       </c>
       <c r="AI54" t="s" s="2">
-        <v>157</v>
+        <v>19</v>
       </c>
       <c r="AJ54" t="s" s="2">
         <v>104</v>
@@ -8504,10 +8456,10 @@
         <v>19</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>499</v>
+        <v>489</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>500</v>
+        <v>490</v>
       </c>
       <c r="AO54" t="s" s="2">
         <v>19</v>
@@ -8518,10 +8470,10 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>501</v>
+        <v>491</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>501</v>
+        <v>491</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8544,13 +8496,13 @@
         <v>19</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>223</v>
+        <v>216</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>225</v>
+        <v>218</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" s="2"/>
@@ -8601,7 +8553,7 @@
         <v>19</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>226</v>
+        <v>219</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>80</v>
@@ -8625,7 +8577,7 @@
         <v>19</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>227</v>
+        <v>220</v>
       </c>
       <c r="AO55" t="s" s="2">
         <v>19</v>
@@ -8636,10 +8588,10 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>502</v>
+        <v>492</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>502</v>
+        <v>492</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8668,7 +8620,7 @@
         <v>139</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>229</v>
+        <v>222</v>
       </c>
       <c r="N56" t="s" s="2">
         <v>141</v>
@@ -8709,19 +8661,19 @@
         <v>19</v>
       </c>
       <c r="AB56" t="s" s="2">
-        <v>142</v>
+        <v>19</v>
       </c>
       <c r="AC56" t="s" s="2">
-        <v>143</v>
+        <v>19</v>
       </c>
       <c r="AD56" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AE56" t="s" s="2">
-        <v>144</v>
+        <v>19</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>80</v>
@@ -8733,7 +8685,7 @@
         <v>19</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="AK56" t="s" s="2">
         <v>19</v>
@@ -8745,7 +8697,7 @@
         <v>19</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>227</v>
+        <v>220</v>
       </c>
       <c r="AO56" t="s" s="2">
         <v>19</v>
@@ -8756,14 +8708,14 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>503</v>
+        <v>493</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>503</v>
+        <v>493</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
-        <v>435</v>
+        <v>430</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
@@ -8785,16 +8737,16 @@
         <v>138</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>436</v>
+        <v>431</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>437</v>
+        <v>432</v>
       </c>
       <c r="N57" t="s" s="2">
         <v>141</v>
       </c>
       <c r="O57" t="s" s="2">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>19</v>
@@ -8843,7 +8795,7 @@
         <v>19</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>438</v>
+        <v>433</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>80</v>
@@ -8855,7 +8807,7 @@
         <v>19</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="AK57" t="s" s="2">
         <v>19</v>
@@ -8878,10 +8830,10 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>504</v>
+        <v>494</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>504</v>
+        <v>494</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8904,19 +8856,19 @@
         <v>93</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>505</v>
+        <v>495</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>506</v>
+        <v>496</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>507</v>
+        <v>497</v>
       </c>
       <c r="O58" t="s" s="2">
-        <v>212</v>
+        <v>205</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>19</v>
@@ -8941,13 +8893,13 @@
         <v>19</v>
       </c>
       <c r="X58" t="s" s="2">
-        <v>213</v>
+        <v>206</v>
       </c>
       <c r="Y58" t="s" s="2">
-        <v>214</v>
+        <v>207</v>
       </c>
       <c r="Z58" t="s" s="2">
-        <v>215</v>
+        <v>208</v>
       </c>
       <c r="AA58" t="s" s="2">
         <v>19</v>
@@ -8965,7 +8917,7 @@
         <v>19</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>504</v>
+        <v>494</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>92</v>
@@ -8974,7 +8926,7 @@
         <v>92</v>
       </c>
       <c r="AI58" t="s" s="2">
-        <v>157</v>
+        <v>19</v>
       </c>
       <c r="AJ58" t="s" s="2">
         <v>104</v>
@@ -8983,16 +8935,16 @@
         <v>19</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>508</v>
+        <v>498</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>218</v>
+        <v>211</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>219</v>
+        <v>212</v>
       </c>
       <c r="AO58" t="s" s="2">
-        <v>220</v>
+        <v>213</v>
       </c>
       <c r="AP58" t="s" s="2">
         <v>19</v>
@@ -9000,10 +8952,10 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>509</v>
+        <v>499</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>509</v>
+        <v>499</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9026,19 +8978,19 @@
         <v>93</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>346</v>
+        <v>341</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>510</v>
+        <v>500</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>348</v>
+        <v>343</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>511</v>
+        <v>501</v>
       </c>
       <c r="O59" t="s" s="2">
-        <v>350</v>
+        <v>345</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>19</v>
@@ -9087,7 +9039,7 @@
         <v>19</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>509</v>
+        <v>499</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>80</v>
@@ -9096,7 +9048,7 @@
         <v>92</v>
       </c>
       <c r="AI59" t="s" s="2">
-        <v>157</v>
+        <v>19</v>
       </c>
       <c r="AJ59" t="s" s="2">
         <v>104</v>
@@ -9105,27 +9057,27 @@
         <v>19</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>512</v>
+        <v>502</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>353</v>
+        <v>348</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>354</v>
+        <v>349</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AP59" t="s" s="2">
-        <v>355</v>
+        <v>350</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>513</v>
+        <v>503</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>513</v>
+        <v>503</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9148,19 +9100,19 @@
         <v>19</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>514</v>
+        <v>504</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>515</v>
+        <v>505</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>516</v>
+        <v>506</v>
       </c>
       <c r="O60" t="s" s="2">
-        <v>360</v>
+        <v>355</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>19</v>
@@ -9185,13 +9137,13 @@
         <v>19</v>
       </c>
       <c r="X60" t="s" s="2">
-        <v>361</v>
+        <v>356</v>
       </c>
       <c r="Y60" t="s" s="2">
-        <v>362</v>
+        <v>357</v>
       </c>
       <c r="Z60" t="s" s="2">
-        <v>363</v>
+        <v>358</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>19</v>
@@ -9209,7 +9161,7 @@
         <v>19</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>513</v>
+        <v>503</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>80</v>
@@ -9218,7 +9170,7 @@
         <v>92</v>
       </c>
       <c r="AI60" t="s" s="2">
-        <v>364</v>
+        <v>359</v>
       </c>
       <c r="AJ60" t="s" s="2">
         <v>104</v>
@@ -9233,7 +9185,7 @@
         <v>135</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>365</v>
+        <v>360</v>
       </c>
       <c r="AO60" t="s" s="2">
         <v>19</v>
@@ -9244,14 +9196,14 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>517</v>
+        <v>507</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>517</v>
+        <v>507</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
-        <v>367</v>
+        <v>362</v>
       </c>
       <c r="E61" s="2"/>
       <c r="F61" t="s" s="2">
@@ -9270,19 +9222,19 @@
         <v>19</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>369</v>
+        <v>364</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="O61" t="s" s="2">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>19</v>
@@ -9307,13 +9259,13 @@
         <v>19</v>
       </c>
       <c r="X61" t="s" s="2">
-        <v>361</v>
+        <v>356</v>
       </c>
       <c r="Y61" t="s" s="2">
-        <v>372</v>
+        <v>367</v>
       </c>
       <c r="Z61" t="s" s="2">
-        <v>373</v>
+        <v>368</v>
       </c>
       <c r="AA61" t="s" s="2">
         <v>19</v>
@@ -9331,7 +9283,7 @@
         <v>19</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>517</v>
+        <v>507</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>80</v>
@@ -9340,7 +9292,7 @@
         <v>81</v>
       </c>
       <c r="AI61" t="s" s="2">
-        <v>157</v>
+        <v>19</v>
       </c>
       <c r="AJ61" t="s" s="2">
         <v>104</v>
@@ -9349,27 +9301,27 @@
         <v>19</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>374</v>
+        <v>369</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>375</v>
+        <v>370</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>376</v>
+        <v>371</v>
       </c>
       <c r="AO61" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AP61" t="s" s="2">
-        <v>377</v>
+        <v>372</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>518</v>
+        <v>508</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>518</v>
+        <v>508</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9395,16 +9347,16 @@
         <v>82</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>519</v>
+        <v>509</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>520</v>
+        <v>510</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>427</v>
+        <v>422</v>
       </c>
       <c r="O62" t="s" s="2">
-        <v>428</v>
+        <v>423</v>
       </c>
       <c r="P62" t="s" s="2">
         <v>19</v>
@@ -9453,7 +9405,7 @@
         <v>19</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>518</v>
+        <v>508</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>80</v>
@@ -9465,7 +9417,7 @@
         <v>19</v>
       </c>
       <c r="AJ62" t="s" s="2">
-        <v>19</v>
+        <v>104</v>
       </c>
       <c r="AK62" t="s" s="2">
         <v>19</v>
@@ -9474,10 +9426,10 @@
         <v>19</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>430</v>
+        <v>425</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>431</v>
+        <v>426</v>
       </c>
       <c r="AO62" t="s" s="2">
         <v>19</v>

--- a/StructureDefinition-VunsPneumoBio.xlsx
+++ b/StructureDefinition-VunsPneumoBio.xlsx
@@ -78,7 +78,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Profil pour les biologies d'intérêt pneumologique</t>
+    <t>Profile for significant laboratory results in the scope of chronic respiratory disease remote monitoring</t>
   </si>
   <si>
     <t>Purpose</t>

--- a/StructureDefinition-VunsPneumoBio.xlsx
+++ b/StructureDefinition-VunsPneumoBio.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.2</t>
+    <t>0.2.0</t>
   </si>
   <si>
     <t>Name</t>

--- a/StructureDefinition-VunsPneumoBio.xlsx
+++ b/StructureDefinition-VunsPneumoBio.xlsx
@@ -87,7 +87,7 @@
     <t>Copyright</t>
   </si>
   <si>
-    <t>RM@H IG (C) 2025-2025 University Hospital of Liege, GSI Department, Belgium. This implementation guide is free software: you can redistribute it and/or modify it under the terms of the GNU General Public License as published by the Free Software Foundation, either version 3 of the License, or (at your option) any later version. This program is distributed in the hope that it will be useful, but WITHOUT ANY WARRANTY; without even the implied warranty of MERCHANTABILITY or FITNESS FOR A PARTICULAR PURPOSE. See the GNU General Public License for more details. You should have received a copy of the GNU General Public License along with this program. If not, see &lt;http://www.gnu.org/licenses/&gt;.</t>
+    <t>VUNS IG (C) 2025-2025 University Hospital of Liege, GSI Department, Belgium. This implementation guide is free software: you can redistribute it and/or modify it under the terms of the GNU General Public License as published by the Free Software Foundation, either version 3 of the License, or (at your option) any later version. This program is distributed in the hope that it will be useful, but WITHOUT ANY WARRANTY; without even the implied warranty of MERCHANTABILITY or FITNESS FOR A PARTICULAR PURPOSE. See the GNU General Public License for more details. You should have received a copy of the GNU General Public License along with this program. If not, see &lt;http://www.gnu.org/licenses/&gt;.</t>
   </si>
   <si>
     <t>FHIR Version</t>
